--- a/Result/profitability/2485.xlsx
+++ b/Result/profitability/2485.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08124999999999999</v>
+        <v>0.04625000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.34375</v>
+        <v>4.751250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.17875</v>
+        <v>0.29</v>
       </c>
       <c r="N3" t="n">
-        <v>6.49875</v>
+        <v>13.2075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4475</v>
+        <v>0.54125</v>
       </c>
       <c r="N4" t="n">
-        <v>14.9475</v>
+        <v>18.405</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6487499999999999</v>
+        <v>0.7537499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>19.96625</v>
+        <v>23.2175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.21</v>
       </c>
       <c r="M6" t="n">
-        <v>0.88625</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>25.2575</v>
+        <v>24.975</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.975</v>
+        <v>0.94875</v>
       </c>
       <c r="N7" t="n">
-        <v>26.4675</v>
+        <v>26.36375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03125</v>
+        <v>0.99875</v>
       </c>
       <c r="N8" t="n">
-        <v>28.3275</v>
+        <v>27.32250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0.965</v>
+        <v>0.9650000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>27.5275</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>909</v>
+      </c>
+      <c r="D75" t="n">
+        <v>778</v>
+      </c>
+      <c r="E75" t="n">
+        <v>131</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>39</v>
+      </c>
+      <c r="K75" t="n">
+        <v>47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-6.671250000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6341463414634146</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.357492218763895</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.217391304347826</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
